--- a/data/trans_bre/P44-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P44-Edad-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -586,7 +586,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -596,32 +596,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4,67</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-37,71</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-57,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-60,63%</t>
         </is>
       </c>
     </row>
@@ -634,39 +634,39 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,69; 5,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,77; -0,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-63,36; -4,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-41,53; 157,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,46; -5,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-76,16; -15,11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -676,32 +676,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1,6</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3,35</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3,59</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-16,85%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-30,53%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-10,6%</t>
         </is>
       </c>
     </row>
@@ -714,39 +714,39 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,25; 2,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,36; 0,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,4; 0,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-50,66; 30,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-56,35; 6,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-22,86; 3,08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -756,32 +756,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1,35</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4,64</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-21,9</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-12,41%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-34,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-47,72%</t>
         </is>
       </c>
     </row>
@@ -794,39 +794,39 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,06; 3,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,53; 0,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-38,37; -7,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-48,55; 41,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-58,0; 4,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-79,64; -17,31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -836,32 +836,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>-5,75</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-4,67</t>
+          <t>-6,57</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-37,71</t>
+          <t>-9,27</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>-51,16%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-57,6%</t>
+          <t>-41,41%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-60,63%</t>
+          <t>-25,62%</t>
         </is>
       </c>
     </row>
@@ -874,39 +874,39 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 5,48</t>
+          <t>-10,97; -1,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,63; -0,97</t>
+          <t>-12,46; -1,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,1; -3,69</t>
+          <t>-14,43; -4,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,55; 162,03</t>
+          <t>-74,32; -10,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-81,72; -13,48</t>
+          <t>-65,3; -8,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-75,45; -13,08</t>
+          <t>-36,55; -12,22</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-1,6</t>
+          <t>-2,03</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-3,35</t>
+          <t>-4,3</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,59</t>
+          <t>-19,13</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-16,85%</t>
+          <t>-21,28%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-30,53%</t>
+          <t>-36,54%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-10,6%</t>
+          <t>-41,9%</t>
         </is>
       </c>
     </row>
@@ -954,295 +954,52 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 2,47</t>
+          <t>-4,39; 0,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 0,15</t>
+          <t>-6,49; -2,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 1,46</t>
+          <t>-44,62; -7,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-49,58; 36,65</t>
+          <t>-40,43; 1,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-56,73; 5,4</t>
+          <t>-49,51; -18,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 4,81</t>
+          <t>-70,53; -21,23</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-4,64</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-21,9</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-12,41%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-34,53%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-47,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-6,58; 3,49</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-9,84; -0,06</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-35,86; -7,4</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-47,07; 45,31</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-59,91; 2,66</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-80,04; -16,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-5,75</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-6,57</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-9,27</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-51,16%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-41,41%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-25,62%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-11,35; -1,24</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-11,79; -1,32</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-14,74; -3,84</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-74,78; -10,87</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-64,16; -10,25</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-37,52; -11,58</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-2,03</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-4,3</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-19,13</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-21,28%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-36,54%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-41,9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-4,74; 0,09</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-6,76; -2,17</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-41,06; -8,19</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-41,63; 1,93</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-50,88; -19,52</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-66,99; -22,27</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_bre/P44-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P44-Edad-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-37,71</t>
+          <t>-5,91</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-60,63%</t>
+          <t>-19,3%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 5,25</t>
+          <t>-3,88; 5,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,77; -0,82</t>
+          <t>-8,29; -0,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-63,36; -4,24</t>
+          <t>-13,14; 0,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-41,53; 157,06</t>
+          <t>-44,54; 161,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-80,46; -5,59</t>
+          <t>-80,22; -4,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-76,16; -15,11</t>
+          <t>-37,59; 1,74</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-3,59</t>
+          <t>-2,57</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-10,6%</t>
+          <t>-7,78%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 2,23</t>
+          <t>-6,38; 2,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 0,47</t>
+          <t>-7,13; 0,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 0,99</t>
+          <t>-7,65; 2,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,66; 30,33</t>
+          <t>-51,92; 33,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,35; 6,58</t>
+          <t>-56,21; 8,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 3,08</t>
+          <t>-21,31; 6,85</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-21,9</t>
+          <t>-7,95</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-47,72%</t>
+          <t>-17,65%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 3,07</t>
+          <t>-6,8; 3,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 0,27</t>
+          <t>-9,59; 0,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-38,37; -7,65</t>
+          <t>-13,12; -2,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-48,55; 41,33</t>
+          <t>-48,04; 44,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-58,0; 4,03</t>
+          <t>-59,56; 4,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-79,64; -17,31</t>
+          <t>-27,52; -5,61</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-9,27</t>
+          <t>-8,61</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-25,62%</t>
+          <t>-23,96%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,97; -1,47</t>
+          <t>-10,78; -1,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,46; -1,31</t>
+          <t>-12,27; -1,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,43; -4,1</t>
+          <t>-13,89; -2,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-74,32; -10,41</t>
+          <t>-74,13; -16,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,3; -8,32</t>
+          <t>-64,49; -10,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,55; -12,22</t>
+          <t>-35,83; -8,8</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-19,13</t>
+          <t>-5,84</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-41,9%</t>
+          <t>-16,18%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 0,09</t>
+          <t>-4,35; 0,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,49; -2,01</t>
+          <t>-6,55; -2,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-44,62; -7,68</t>
+          <t>-8,49; -3,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-40,43; 1,06</t>
+          <t>-39,97; 3,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-49,51; -18,48</t>
+          <t>-50,87; -19,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-70,53; -21,23</t>
+          <t>-22,73; -8,63</t>
         </is>
       </c>
     </row>
